--- a/modelo-planilha-contatos.xlsx
+++ b/modelo-planilha-contatos.xlsx
@@ -474,29 +474,29 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nome</t>
+          <t>Telefone</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>31987654321</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>Maria</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>31987654321</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -508,12 +508,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Joao</t>
+          <t>31912345678</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>31912345678</t>
+          <t>João</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>1. Nao mude os titulos da primeira linha da aba Contatos (nome, telefone, valor).</t>
+          <t>1. Nao mude os titulos da primeira linha da aba Contatos (Telefone, A, B).</t>
         </is>
       </c>
     </row>
@@ -591,6 +591,8 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/modelo-planilha-contatos.xlsx
+++ b/modelo-planilha-contatos.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Texto 1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Texto 2</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>1. Nao mude os titulos da primeira linha da aba Contatos (Telefone, A, B).</t>
+          <t>1. Nao mude os titulos da primeira linha da aba Contatos (Telefone, Texto 1, Texto 2).</t>
         </is>
       </c>
     </row>
@@ -591,8 +591,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
